--- a/AAII_Financials/Yearly/SRHBY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SRHBY_YR_FIN.xlsx
@@ -305,7 +305,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -347,7 +347,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -735,7 +735,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>1781200</v>
+        <v>1223900</v>
       </c>
       <c r="E9" s="3">
         <v>1267100</v>
@@ -762,7 +762,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>-46300</v>
+        <v>511000</v>
       </c>
       <c r="E10" s="3">
         <v>530800</v>
@@ -856,13 +856,13 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="E14" s="3">
-        <v>12400</v>
+        <v>7100</v>
       </c>
       <c r="F14" s="3">
-        <v>67600</v>
+        <v>44400</v>
       </c>
       <c r="G14" s="3">
         <v>-3000</v>
@@ -883,7 +883,7 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>156100</v>
+        <v>172900</v>
       </c>
       <c r="E15" s="3">
         <v>182700</v>
@@ -920,13 +920,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1570500</v>
+        <v>1569800</v>
       </c>
       <c r="E17" s="3">
-        <v>1626300</v>
+        <v>1626100</v>
       </c>
       <c r="F17" s="3">
-        <v>1597100</v>
+        <v>1597000</v>
       </c>
       <c r="G17" s="3">
         <v>1347100</v>
@@ -947,13 +947,13 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>164400</v>
+        <v>165100</v>
       </c>
       <c r="E18" s="3">
-        <v>171600</v>
+        <v>171800</v>
       </c>
       <c r="F18" s="3">
-        <v>138600</v>
+        <v>138700</v>
       </c>
       <c r="G18" s="3">
         <v>167900</v>
@@ -987,13 +987,13 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-2900</v>
+        <v>-1900</v>
       </c>
       <c r="E20" s="3">
-        <v>-6200</v>
+        <v>-800</v>
       </c>
       <c r="F20" s="3">
-        <v>-24400</v>
+        <v>-1000</v>
       </c>
       <c r="G20" s="3">
         <v>-800</v>
@@ -1014,13 +1014,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>323500</v>
+        <v>339800</v>
       </c>
       <c r="E21" s="3">
-        <v>360500</v>
+        <v>355200</v>
       </c>
       <c r="F21" s="3">
-        <v>361700</v>
+        <v>338400</v>
       </c>
       <c r="G21" s="3">
         <v>375700</v>
@@ -1041,7 +1041,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>31500</v>
+        <v>30800</v>
       </c>
       <c r="E22" s="3">
         <v>29300</v>
@@ -1095,7 +1095,7 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>27300</v>
+        <v>27200</v>
       </c>
       <c r="E24" s="3">
         <v>38500</v>
@@ -1176,7 +1176,7 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>111800</v>
+        <v>111900</v>
       </c>
       <c r="E27" s="3">
         <v>107300</v>
@@ -1311,13 +1311,13 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>2900</v>
+        <v>1900</v>
       </c>
       <c r="E32" s="3">
-        <v>6200</v>
+        <v>800</v>
       </c>
       <c r="F32" s="3">
-        <v>24400</v>
+        <v>1000</v>
       </c>
       <c r="G32" s="3">
         <v>800</v>
@@ -1338,7 +1338,7 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>117600</v>
+        <v>117700</v>
       </c>
       <c r="E33" s="3">
         <v>113300</v>
@@ -1392,7 +1392,7 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>117600</v>
+        <v>117700</v>
       </c>
       <c r="E35" s="3">
         <v>113300</v>
@@ -1504,7 +1504,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>5900</v>
       </c>
       <c r="E42" s="3">
         <v>5600</v>
@@ -1531,7 +1531,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>678700</v>
+        <v>587100</v>
       </c>
       <c r="E43" s="3">
         <v>468800</v>
@@ -1585,7 +1585,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>10000</v>
+        <v>12200</v>
       </c>
       <c r="E45" s="3">
         <v>79500</v>
@@ -1881,7 +1881,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>579300</v>
+        <v>155900</v>
       </c>
       <c r="E57" s="3">
         <v>152700</v>
@@ -1935,7 +1935,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>70500</v>
+        <v>86800</v>
       </c>
       <c r="E59" s="3">
         <v>144500</v>
@@ -2016,7 +2016,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>36700</v>
+        <v>35900</v>
       </c>
       <c r="E62" s="3">
         <v>36900</v>
@@ -2124,7 +2124,7 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1724600</v>
+        <v>1724500</v>
       </c>
       <c r="E66" s="3">
         <v>1765000</v>
@@ -2272,7 +2272,7 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>316300</v>
+        <v>316200</v>
       </c>
       <c r="E72" s="3">
         <v>304000</v>
@@ -2466,7 +2466,7 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>117600</v>
+        <v>117700</v>
       </c>
       <c r="E81" s="3">
         <v>113300</v>
@@ -2506,7 +2506,7 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>172900</v>
+        <v>127000</v>
       </c>
       <c r="E83" s="3">
         <v>130400</v>
@@ -2829,7 +2829,7 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>96400</v>
+        <v>96500</v>
       </c>
       <c r="E96" s="3">
         <v>71400</v>
@@ -2937,7 +2937,7 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-162500</v>
+        <v>-163000</v>
       </c>
       <c r="E100" s="3">
         <v>-158900</v>
@@ -2964,7 +2964,7 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-200</v>
+        <v>300</v>
       </c>
       <c r="E101" s="3">
         <v>200</v>
